--- a/recipients_outlook.xlsx
+++ b/recipients_outlook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/mailmerge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4845D4A8-548C-A04C-B664-33C30ACD7719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55670ABA-73F7-5542-A90F-FDDE109F3062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>Email</t>
   </si>
@@ -40,29 +40,62 @@
     <t>BCC</t>
   </si>
   <si>
-    <t>Bảo Phương</t>
-  </si>
-  <si>
-    <t>minhquando43730@gmail.com</t>
-  </si>
-  <si>
-    <t>Minh Quân</t>
-  </si>
-  <si>
-    <t>minhquando59@gmail.com</t>
-  </si>
-  <si>
-    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/Võ Thị Thanh Lam - 24.7/DoMinhQuan.pdf</t>
-  </si>
-  <si>
-    <t>[BOOKMEDI] Đơn hàng của {{Ten}} đã được giao thành công + QUÀ TẶNG độc quyền từ Bookmedi!!!!!🎁🎁🎁</t>
+    <t>info@cdimex.com.vn</t>
+  </si>
+  <si>
+    <t>Kết quả bài thi Versant Professional English Test  - {{Ten}}</t>
+  </si>
+  <si>
+    <t>Dương Minh Trí</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Thảo Vy</t>
+  </si>
+  <si>
+    <t>Nguyễn Mai Phương Nam</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Nhật Tiến</t>
+  </si>
+  <si>
+    <t>Trần Thạch Thảo</t>
+  </si>
+  <si>
+    <t>duongtri642002@gmail.com</t>
+  </si>
+  <si>
+    <t>ngnhngthaovy2810@gmail.com</t>
+  </si>
+  <si>
+    <t>nguyenmaiphuongnam2906@gmail.com</t>
+  </si>
+  <si>
+    <t>tiennguyenpoy0000@gmail.com</t>
+  </si>
+  <si>
+    <t>Thaotran.smc@gmail.com</t>
+  </si>
+  <si>
+    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/uploads/SK_ScoreReport_36085131_Trần Thạch Thảo.pdf</t>
+  </si>
+  <si>
+    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/uploads/SK_ScoreReport_38712918_Nguyễn Mai Phương Nam.pdf</t>
+  </si>
+  <si>
+    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/uploads/SK_ScoreReport_48301414_Nguyễn Hoàng Thảo Vy.pdf</t>
+  </si>
+  <si>
+    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/uploads/SK_ScoreReport_52162894_Dương Minh Trí.pdf</t>
+  </si>
+  <si>
+    <t>/Users/dominhquan/Desktop/Cdimex/mailmerge/uploads/SK_ScoreReport_74783671_Nguyễn Văn Nhật Tiến.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,18 +104,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,14 +158,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -433,10 +478,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="98.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -459,39 +508,92 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
+      <c r="E6" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{41C5AE45-2A64-0D43-A2F1-5E70A515C2F6}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{AE932619-A0D5-604A-B0A4-6EAC1D00EAE2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>